--- a/output/NIFTY50_shareholder_categories.xlsx
+++ b/output/NIFTY50_shareholder_categories.xlsx
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -876,19 +876,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
         <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -946,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -961,13 +961,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1179,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1431,13 +1431,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="V11" t="n">
-        <v>2</v>
-      </c>
       <c r="W11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1498,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1513,10 +1513,10 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1641,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1656,13 +1656,13 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -1671,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1720,7 +1720,7 @@
         <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1750,10 +1750,10 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1908,10 +1908,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
         <v>2</v>
@@ -2063,13 +2063,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2097,13 +2097,13 @@
         <v>53</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>10000000331</v>
+        <v>1002568002</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>3331607557</v>
+        <v>1410603325</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.3331607446723793</v>
+        <v>1.406990171425798</v>
       </c>
       <c r="I20" t="n">
         <v>46</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -4493,29 +4493,46 @@
           <t>New World Fund Inc</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="n">
         <v>3706104</v>
       </c>
       <c r="E47" s="2" t="n"/>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="n"/>
-      <c r="I47" s="12" t="n"/>
-      <c r="J47" s="12" t="n"/>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="n"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1073330/000005193118000997/nwf_nq.htm</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4528,29 +4545,46 @@
           <t>Government Of Singapore</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="n">
         <v>2923691</v>
       </c>
       <c r="E48" s="2" t="n"/>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="n"/>
-      <c r="I48" s="12" t="n"/>
-      <c r="J48" s="12" t="n"/>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="n"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:L48"/>
@@ -9127,29 +9161,46 @@
           <t>Artisan International Value Fund</t>
         </is>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D65" s="2" t="n">
         <v>53387154</v>
       </c>
       <c r="E65" s="2" t="n"/>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G65" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H65" s="12" t="n"/>
-      <c r="I65" s="12" t="n"/>
-      <c r="J65" s="12" t="n"/>
-      <c r="K65" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L65" s="12" t="n"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/935015/000119312511059568/d497.htm</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10015,29 +10066,46 @@
           <t>Government of Singapore</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
         <v>8213760</v>
       </c>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="n"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10052,46 +10120,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Foreign Pension Fund</t>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
         <v>4775432</v>
       </c>
       <c r="E19" s="2" t="n"/>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>pension_fund</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>pension_assets</t>
-        </is>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nbim.no/</t>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Government_Pension_Fund_of_Norway</t>
         </is>
       </c>
     </row>
@@ -10838,10 +10902,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -10856,29 +10930,46 @@
           <t>Tobacco Manufacturers (India) Limited</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
         <v>2228495863</v>
       </c>
       <c r="E14" s="2" t="n"/>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="n"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>IM</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>operating_company_treasury</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1303523/000130352326000017/a2025fy-ex8xsubsidiariesun.htm</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10891,29 +10982,46 @@
           <t>Myddleton Investment Company Limited</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="n">
         <v>486311940</v>
       </c>
       <c r="E15" s="2" t="n"/>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="n"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://bat.com/content/dam/batcom/global/main-nav/investors-and-reporting/reporting/combined-annual-and-esg-report/previous-annual-reporting/uk-company-reporting/Myddleton_Investment_Company_Limited_-_Annual_Report_2022.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10926,29 +11034,46 @@
           <t>Rothmans International Enterprises Limited</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="n">
         <v>154954890</v>
       </c>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="n"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>operating_company_treasury</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://bat.com/content/dam/batcom/global/main-nav/investors-and-reporting/reporting/combined-annual-and-esg-report/previous-annual-reporting/uk-company-reporting/Rothmans_International_Enterprises_Limited_-_Annual_Report_2024.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10961,29 +11086,46 @@
           <t>GQG Partners Emerging Markets Equity Fund</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="n">
         <v>223800530</v>
       </c>
       <c r="E17" s="2" t="n"/>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="n"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1593547/000119312520267112/d87085dncsr.htm</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10996,29 +11138,46 @@
           <t>Goldman Sachs Trust II-Goldman Sachs GQG Partners International Opportunities Fund</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
         <v>177285000</v>
       </c>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="n"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1557156/000119312516793306/d174361d497.htm</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:L18"/>
@@ -15557,29 +15716,46 @@
           <t>GQG Partners Emerging Markets Equity Fund</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="n">
         <v>24902245</v>
       </c>
       <c r="E57" s="2" t="n"/>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H57" s="12" t="n"/>
-      <c r="I57" s="12" t="n"/>
-      <c r="J57" s="12" t="n"/>
-      <c r="K57" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L57" s="12" t="n"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1593547/000119312520267112/d87085dncsr.htm</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -15644,29 +15820,46 @@
           <t>JFE Steel International Europe B.V</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
+        </is>
+      </c>
       <c r="D59" s="2" t="n">
         <v>366818095</v>
       </c>
       <c r="E59" s="2" t="n"/>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H59" s="12" t="n"/>
-      <c r="I59" s="12" t="n"/>
-      <c r="J59" s="12" t="n"/>
-      <c r="K59" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L59" s="12" t="n"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>operating_company_treasury</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://lei.jpx.co.jp/lei/en/detail.html?lei=3538004SYEDMHPTGRC96</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -15679,29 +15872,46 @@
           <t>Gagandeep Credit Capital Pvt Ltd</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
+        </is>
+      </c>
       <c r="D60" s="2" t="n">
         <v>49550000</v>
       </c>
       <c r="E60" s="2" t="n"/>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G60" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H60" s="12" t="n"/>
-      <c r="I60" s="12" t="n"/>
-      <c r="J60" s="12" t="n"/>
-      <c r="K60" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L60" s="12" t="n"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://www.thecompanycheck.com/company/gagandeep-credit-capital-private-limited/U65990MH1993PTC073769</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -15714,29 +15924,46 @@
           <t>Enam Securities Pvt Ltd</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
+        </is>
+      </c>
       <c r="D61" s="2" t="n">
         <v>27985121</v>
       </c>
       <c r="E61" s="2" t="n"/>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G61" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H61" s="12" t="n"/>
-      <c r="I61" s="12" t="n"/>
-      <c r="J61" s="12" t="n"/>
-      <c r="K61" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L61" s="12" t="n"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://indiafilings.com/search/enam-securities-private-limited-cin-u67120mh2005ptc152297</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -15749,29 +15976,46 @@
           <t>Shamyak Investment Private Limited</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="n">
         <v>26533230</v>
       </c>
       <c r="E62" s="2" t="n"/>
-      <c r="F62" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G62" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H62" s="12" t="n"/>
-      <c r="I62" s="12" t="n"/>
-      <c r="J62" s="12" t="n"/>
-      <c r="K62" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L62" s="12" t="n"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://www.instafinancials.com/company/shamyak-investment-private-limited-u23201mh1983ptc031175/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:L62"/>
@@ -16405,29 +16649,46 @@
           <t>GOVERNMENT OF SINGAPORE</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="n">
         <v>21502855</v>
       </c>
       <c r="E13" s="2" t="n"/>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="n"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16440,29 +16701,46 @@
           <t>L&amp;T EMPLOYEES TRUST</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
         <v>198679507</v>
       </c>
       <c r="E14" s="2" t="n"/>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="n"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sebi.gov.in/sebi-data/docfiles/11754_t.html</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:L14"/>
@@ -18130,7 +18408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -18190,7 +18468,7 @@
         <v>41508906110</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.6163142758676555</v>
+        <v>0.6344092843380742</v>
       </c>
     </row>
     <row r="5">
@@ -18209,45 +18487,45 @@
         <v>8548172071</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.126921207366177</v>
+        <v>0.1306476184072543</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(unclassified)</t>
+          <t>Domestic Insurance</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7206653596</v>
+        <v>6736353540</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.1070026630111014</v>
+        <v>0.1029563442851145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Domestic Insurance</t>
+          <t>Foreign corporate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6736353540</v>
+        <v>3458757632</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.1000197606506769</v>
+        <v>0.0528625820251945</v>
       </c>
     </row>
     <row r="8">
@@ -18266,101 +18544,139 @@
         <v>1096359926</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.01627848905708025</v>
+        <v>0.01675642605920274</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>974531427</v>
+        <v>1042916148</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.01446960874252193</v>
+        <v>0.0159396078837622</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Foreign AMC</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>551440130</v>
+        <v>974531427</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.008187650705722629</v>
+        <v>0.01489443695600275</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Domestic Pension Fund</t>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>546071232</v>
+        <v>934792226</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.008107934596743305</v>
+        <v>0.01428707529728384</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Foreign Pension Fund</t>
+          <t>Domestic Pension Fund</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>546071232</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.008345983837123346</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>181738525</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0.002698410002321086</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>302747858</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.004627104636765985</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>(unclassified)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>279614155</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.004273536274221642</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B15" s="6" t="n">
         <v>553</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C15" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>67350226557</v>
-      </c>
-      <c r="E13" s="8" t="n">
+      <c r="D15" s="7" t="n">
+        <v>65429222325</v>
+      </c>
+      <c r="E15" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18878,29 +19194,46 @@
           <t>Government Of Singapore</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
         <v>197673526</v>
       </c>
       <c r="E11" s="2" t="n"/>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="n"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:L11"/>
@@ -19368,29 +19701,46 @@
           <t>GOVERNMENT OF SINGAPORE</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
         <v>164016397</v>
       </c>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="n"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22820,7 +23170,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Foreign Pension Fund</t>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="D63" s="2" t="n"/>
@@ -22835,39 +23185,35 @@
         <v>105494998</v>
       </c>
       <c r="M63" s="2" t="n"/>
-      <c r="N63" s="12" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="O63" s="12" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="P63" s="12" t="inlineStr">
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="Q63" s="12" t="inlineStr">
-        <is>
-          <t>pension_fund</t>
-        </is>
-      </c>
-      <c r="R63" s="12" t="inlineStr">
-        <is>
-          <t>pension_assets</t>
-        </is>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="T63" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nbim.no/</t>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Government_Pension_Fund_of_Norway</t>
         </is>
       </c>
     </row>
@@ -24016,29 +24362,23 @@
         <v>555000000</v>
       </c>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>filing (token+numeric)</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="n"/>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>SEBI LODR Reg 31 shareholding pattern (Table II - Promoter &amp; Promoter Group), as at 2025-09-30</t>
         </is>
@@ -25954,37 +26294,33 @@
         <v>150607989</v>
       </c>
       <c r="E49" s="2" t="n"/>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>rule:amc+india</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>asset_manager</t>
         </is>
       </c>
-      <c r="J49" s="12" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>managed_funds</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
         <is>
           <t>matched by deterministic name rule</t>
         </is>
@@ -26010,37 +26346,33 @@
         <v>40680381</v>
       </c>
       <c r="E50" s="2" t="n"/>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>rule:amc+india</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>asset_manager</t>
         </is>
       </c>
-      <c r="J50" s="12" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>managed_funds</t>
         </is>
       </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
         <is>
           <t>matched by deterministic name rule</t>
         </is>
@@ -26066,37 +26398,33 @@
         <v>40518952</v>
       </c>
       <c r="E51" s="2" t="n"/>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>rule:amc+india</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>asset_manager</t>
         </is>
       </c>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>managed_funds</t>
         </is>
       </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
         <is>
           <t>matched by deterministic name rule</t>
         </is>
@@ -26122,33 +26450,37 @@
         <v>121567690</v>
       </c>
       <c r="E52" s="2" t="n"/>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>rule:amc+india</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
         <is>
           <t>asset_manager</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="12" t="inlineStr">
         <is>
           <t>managed_funds</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr">
         <is>
           <t>matched by deterministic name rule</t>
         </is>
@@ -26174,33 +26506,37 @@
         <v>137781580</v>
       </c>
       <c r="E53" s="2" t="n"/>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>rule:indian-pension-scheme</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
         <is>
           <t>pension_fund</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="12" t="inlineStr">
         <is>
           <t>pension_assets</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
         <is>
           <t>matched by deterministic name rule</t>
         </is>
@@ -26217,29 +26553,50 @@
           <t>GOVERNMENT OF SINGAPORE</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="D54" s="2" t="n">
-        <v>2134450960</v>
+        <v>213446728</v>
       </c>
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H54" s="12" t="n"/>
-      <c r="I54" s="12" t="n"/>
-      <c r="J54" s="12" t="n"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="L54" s="12" t="n"/>
+      <c r="L54" s="12" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -26252,29 +26609,50 @@
           <t>MACRITCHIE INVESTMENTS PTE LTD</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="n">
         <v>151000005</v>
       </c>
       <c r="E55" s="2" t="n"/>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="n"/>
-      <c r="I55" s="12" t="n"/>
-      <c r="J55" s="12" t="n"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="L55" s="12" t="n"/>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>https://www.crunchbase.com/organization/macritchie-investments</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:L55"/>
@@ -27670,7 +28048,7 @@
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 10 holders to 0.139%</t>
+          <t>stated denominator agrees with 10 of 10 holders to 0.139%</t>
         </is>
       </c>
       <c r="H3" s="9" t="n">
@@ -27721,7 +28099,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 12 holders to 0.054%</t>
+          <t>stated denominator agrees with 12 of 12 holders to 0.054%</t>
         </is>
       </c>
       <c r="H4" s="9" t="n">
@@ -27774,7 +28152,7 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 14 holders to 0.067%</t>
+          <t>stated denominator agrees with 14 of 14 holders to 0.067%</t>
         </is>
       </c>
       <c r="H5" s="9" t="n">
@@ -27825,7 +28203,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 5 holders to 0.081%</t>
+          <t>stated denominator agrees with 5 of 5 holders to 0.081%</t>
         </is>
       </c>
       <c r="H6" s="9" t="n">
@@ -27925,7 +28303,7 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 14 holders to 0.035%</t>
+          <t>stated denominator agrees with 12 of 14 holders to 0.035%</t>
         </is>
       </c>
       <c r="H8" s="9" t="n">
@@ -28079,7 +28457,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 17 holders to 0.044%</t>
+          <t>stated denominator agrees with 15 of 17 holders to 0.044%</t>
         </is>
       </c>
       <c r="H11" s="9" t="n">
@@ -28130,7 +28508,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 16 holders to 0.007%</t>
+          <t>stated denominator agrees with 16 of 16 holders to 0.007%</t>
         </is>
       </c>
       <c r="H12" s="9" t="n">
@@ -28181,7 +28559,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 21 holders to 0.027%</t>
+          <t>stated denominator agrees with 11 of 21 holders to 0.027%</t>
         </is>
       </c>
       <c r="H13" s="9" t="n">
@@ -28232,7 +28610,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 33 holders to 0.230%</t>
+          <t>stated denominator agrees with 18 of 33 holders to 0.230%</t>
         </is>
       </c>
       <c r="H14" s="9" t="n">
@@ -28283,7 +28661,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 12 holders to 0.088%</t>
+          <t>stated denominator agrees with 12 of 12 holders to 0.088%</t>
         </is>
       </c>
       <c r="H15" s="9" t="n">
@@ -28334,7 +28712,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 25 holders to 0.026%</t>
+          <t>stated denominator agrees with 10 of 25 holders to 0.026%</t>
         </is>
       </c>
       <c r="H16" s="9" t="n">
@@ -28385,7 +28763,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 9 holders to 0.007%</t>
+          <t>stated denominator agrees with 9 of 9 holders to 0.007%</t>
         </is>
       </c>
       <c r="H17" s="9" t="n">
@@ -28436,7 +28814,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 10 holders to 0.012%</t>
+          <t>stated denominator agrees with 10 of 10 holders to 0.012%</t>
         </is>
       </c>
       <c r="H18" s="9" t="n">
@@ -28487,7 +28865,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 72 holders to 0.000%</t>
+          <t>stated denominator agrees with 47 of 72 holders to 0.000%</t>
         </is>
       </c>
       <c r="H19" s="9" t="n">
@@ -28535,19 +28913,19 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>10000000331</v>
+        <v>1002568002</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>stated 1,002,568,002.0 disagreed with 8 holders by 897.44%; used the implied 10,000,000,331 (SCRR basis)</t>
+          <t>stated denominator kept: backed by 4 of 8 holders against 3 for the implied 10,000,000,331</t>
         </is>
       </c>
       <c r="H20" s="9" t="n">
         <v>55.36</v>
       </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>unreconciled (-90.0%)</t>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>reconciled (-0.0%)</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
@@ -28690,7 +29068,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>stated denominator agrees with 10 holders to 0.035%</t>
+          <t>stated denominator agrees with 8 of 10 holders to 0.035%</t>
         </is>
       </c>
       <c r="H23" s="9" t="n">
@@ -29343,6 +29721,11 @@
           <t>Government of Singapore</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="n">
         <v>80899294</v>
       </c>
@@ -29355,25 +29738,37 @@
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P10" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q10" s="12" t="n"/>
-      <c r="R10" s="12" t="n"/>
-      <c r="S10" s="12" t="n"/>
-      <c r="T10" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U10" s="12" t="n"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29946,6 +30341,11 @@
           <t>Google International LLC</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="n">
         <v>71176839</v>
       </c>
@@ -29958,25 +30358,37 @@
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
-      <c r="O20" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P20" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q20" s="12" t="n"/>
-      <c r="R20" s="12" t="n"/>
-      <c r="S20" s="12" t="n"/>
-      <c r="T20" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U20" s="12" t="n"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>operating_company_treasury</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1288776/000119312507044494/dex2101.htm</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -29992,6 +30404,11 @@
       <c r="C21" t="inlineStr">
         <is>
           <t>Government of Singapore - E</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -30008,23 +30425,39 @@
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q21" s="12" t="n"/>
-      <c r="R21" s="12" t="n"/>
-      <c r="S21" s="12" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q21" s="12" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="R21" s="12" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S21" s="12" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="U21" s="12" t="n"/>
+      <c r="U21" s="12" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -30044,7 +30477,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Foreign Pension Fund</t>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
@@ -30059,39 +30492,35 @@
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
-      <c r="O22" s="12" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="P22" s="12" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="Q22" s="12" t="inlineStr">
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="R22" s="12" t="inlineStr">
-        <is>
-          <t>pension_fund</t>
-        </is>
-      </c>
-      <c r="S22" s="12" t="inlineStr">
-        <is>
-          <t>pension_assets</t>
-        </is>
-      </c>
-      <c r="T22" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U22" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nbim.no/</t>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Government_Pension_Fund_of_Norway</t>
         </is>
       </c>
     </row>
@@ -30853,7 +31282,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Foreign Pension Fund</t>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
@@ -30868,39 +31297,35 @@
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
       <c r="N35" s="2" t="n"/>
-      <c r="O35" s="12" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="P35" s="12" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="Q35" s="12" t="inlineStr">
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="R35" s="12" t="inlineStr">
-        <is>
-          <t>pension_fund</t>
-        </is>
-      </c>
-      <c r="S35" s="12" t="inlineStr">
-        <is>
-          <t>pension_assets</t>
-        </is>
-      </c>
-      <c r="T35" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U35" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nbim.no/</t>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Government_Pension_Fund_of_Norway</t>
         </is>
       </c>
     </row>
@@ -30918,6 +31343,11 @@
       <c r="C36" t="inlineStr">
         <is>
           <t>Vanguard Total International Stock Index Fund</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
@@ -30932,25 +31362,37 @@
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="n"/>
-      <c r="O36" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P36" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q36" s="12" t="n"/>
-      <c r="R36" s="12" t="n"/>
-      <c r="S36" s="12" t="n"/>
-      <c r="T36" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U36" s="12" t="n"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/736054/000168386322001087/f11043d1.htm</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -33883,6 +34325,11 @@
           <t>New World Fund Inc</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="E88" s="2" t="n"/>
       <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="n">
@@ -33895,25 +34342,37 @@
       <c r="L88" s="2" t="n"/>
       <c r="M88" s="2" t="n"/>
       <c r="N88" s="2" t="n"/>
-      <c r="O88" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P88" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q88" s="12" t="n"/>
-      <c r="R88" s="12" t="n"/>
-      <c r="S88" s="12" t="n"/>
-      <c r="T88" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U88" s="12" t="n"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1073330/000005193118000997/nwf_nq.htm</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -33929,6 +34388,11 @@
       <c r="C89" t="inlineStr">
         <is>
           <t>Government Of Singapore</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="E89" s="2" t="n"/>
@@ -33943,25 +34407,37 @@
       <c r="L89" s="2" t="n"/>
       <c r="M89" s="2" t="n"/>
       <c r="N89" s="2" t="n"/>
-      <c r="O89" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P89" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q89" s="12" t="n"/>
-      <c r="R89" s="12" t="n"/>
-      <c r="S89" s="12" t="n"/>
-      <c r="T89" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U89" s="12" t="n"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -39706,6 +40182,11 @@
           <t>Artisan International Value Fund</t>
         </is>
       </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="E195" s="2" t="n">
         <v>53387154</v>
       </c>
@@ -39718,25 +40199,37 @@
       <c r="L195" s="2" t="n"/>
       <c r="M195" s="2" t="n"/>
       <c r="N195" s="2" t="n"/>
-      <c r="O195" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P195" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q195" s="12" t="n"/>
-      <c r="R195" s="12" t="n"/>
-      <c r="S195" s="12" t="n"/>
-      <c r="T195" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U195" s="12" t="n"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/935015/000119312511059568/d497.htm</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -40714,6 +41207,11 @@
           <t>Government of Singapore</t>
         </is>
       </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="E212" s="2" t="n">
         <v>8213760</v>
       </c>
@@ -40726,25 +41224,37 @@
       <c r="L212" s="2" t="n"/>
       <c r="M212" s="2" t="n"/>
       <c r="N212" s="2" t="n"/>
-      <c r="O212" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P212" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q212" s="12" t="n"/>
-      <c r="R212" s="12" t="n"/>
-      <c r="S212" s="12" t="n"/>
-      <c r="T212" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U212" s="12" t="n"/>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -40764,7 +41274,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Foreign Pension Fund</t>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="E213" s="2" t="n">
@@ -40779,39 +41289,35 @@
       <c r="L213" s="2" t="n"/>
       <c r="M213" s="2" t="n"/>
       <c r="N213" s="2" t="n"/>
-      <c r="O213" s="12" t="inlineStr">
+      <c r="O213" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="P213" s="12" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="Q213" s="12" t="inlineStr">
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="R213" s="12" t="inlineStr">
-        <is>
-          <t>pension_fund</t>
-        </is>
-      </c>
-      <c r="S213" s="12" t="inlineStr">
-        <is>
-          <t>pension_assets</t>
-        </is>
-      </c>
-      <c r="T213" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U213" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nbim.no/</t>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Government_Pension_Fund_of_Norway</t>
         </is>
       </c>
     </row>
@@ -41626,10 +42132,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -41647,6 +42163,11 @@
       <c r="C227" t="inlineStr">
         <is>
           <t>Tobacco Manufacturers (India) Limited</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
         </is>
       </c>
       <c r="E227" s="2" t="n"/>
@@ -41661,25 +42182,37 @@
       <c r="L227" s="2" t="n"/>
       <c r="M227" s="2" t="n"/>
       <c r="N227" s="2" t="n"/>
-      <c r="O227" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P227" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q227" s="12" t="n"/>
-      <c r="R227" s="12" t="n"/>
-      <c r="S227" s="12" t="n"/>
-      <c r="T227" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U227" s="12" t="n"/>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>IM</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>operating_company_treasury</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1303523/000130352326000017/a2025fy-ex8xsubsidiariesun.htm</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -41695,6 +42228,11 @@
       <c r="C228" t="inlineStr">
         <is>
           <t>Myddleton Investment Company Limited</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
         </is>
       </c>
       <c r="E228" s="2" t="n"/>
@@ -41709,25 +42247,37 @@
       <c r="L228" s="2" t="n"/>
       <c r="M228" s="2" t="n"/>
       <c r="N228" s="2" t="n"/>
-      <c r="O228" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P228" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q228" s="12" t="n"/>
-      <c r="R228" s="12" t="n"/>
-      <c r="S228" s="12" t="n"/>
-      <c r="T228" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U228" s="12" t="n"/>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>https://bat.com/content/dam/batcom/global/main-nav/investors-and-reporting/reporting/combined-annual-and-esg-report/previous-annual-reporting/uk-company-reporting/Myddleton_Investment_Company_Limited_-_Annual_Report_2022.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -41743,6 +42293,11 @@
       <c r="C229" t="inlineStr">
         <is>
           <t>Rothmans International Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
         </is>
       </c>
       <c r="E229" s="2" t="n"/>
@@ -41757,25 +42312,37 @@
       <c r="L229" s="2" t="n"/>
       <c r="M229" s="2" t="n"/>
       <c r="N229" s="2" t="n"/>
-      <c r="O229" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P229" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q229" s="12" t="n"/>
-      <c r="R229" s="12" t="n"/>
-      <c r="S229" s="12" t="n"/>
-      <c r="T229" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U229" s="12" t="n"/>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>operating_company_treasury</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr"/>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>https://bat.com/content/dam/batcom/global/main-nav/investors-and-reporting/reporting/combined-annual-and-esg-report/previous-annual-reporting/uk-company-reporting/Rothmans_International_Enterprises_Limited_-_Annual_Report_2024.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -41791,6 +42358,11 @@
       <c r="C230" t="inlineStr">
         <is>
           <t>GQG Partners Emerging Markets Equity Fund</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="E230" s="2" t="n"/>
@@ -41805,25 +42377,37 @@
       <c r="L230" s="2" t="n"/>
       <c r="M230" s="2" t="n"/>
       <c r="N230" s="2" t="n"/>
-      <c r="O230" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P230" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q230" s="12" t="n"/>
-      <c r="R230" s="12" t="n"/>
-      <c r="S230" s="12" t="n"/>
-      <c r="T230" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U230" s="12" t="n"/>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1593547/000119312520267112/d87085dncsr.htm</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -41839,6 +42423,11 @@
       <c r="C231" t="inlineStr">
         <is>
           <t>Goldman Sachs Trust II-Goldman Sachs GQG Partners International Opportunities Fund</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="E231" s="2" t="n"/>
@@ -41853,25 +42442,37 @@
       <c r="L231" s="2" t="n"/>
       <c r="M231" s="2" t="n"/>
       <c r="N231" s="2" t="n"/>
-      <c r="O231" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P231" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q231" s="12" t="n"/>
-      <c r="R231" s="12" t="n"/>
-      <c r="S231" s="12" t="n"/>
-      <c r="T231" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U231" s="12" t="n"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr"/>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1557156/000119312516793306/d174361d497.htm</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -47539,6 +48140,11 @@
           <t>GQG Partners Emerging Markets Equity Fund</t>
         </is>
       </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="E334" s="2" t="n">
         <v>24902245</v>
       </c>
@@ -47551,25 +48157,37 @@
       <c r="L334" s="2" t="n"/>
       <c r="M334" s="2" t="n"/>
       <c r="N334" s="2" t="n"/>
-      <c r="O334" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P334" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q334" s="12" t="n"/>
-      <c r="R334" s="12" t="n"/>
-      <c r="S334" s="12" t="n"/>
-      <c r="T334" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U334" s="12" t="n"/>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr"/>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1593547/000119312520267112/d87085dncsr.htm</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -47652,6 +48270,11 @@
           <t>JFE Steel International Europe B.V</t>
         </is>
       </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
+        </is>
+      </c>
       <c r="E336" s="2" t="n">
         <v>366818095</v>
       </c>
@@ -47664,25 +48287,37 @@
       <c r="L336" s="2" t="n"/>
       <c r="M336" s="2" t="n"/>
       <c r="N336" s="2" t="n"/>
-      <c r="O336" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P336" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q336" s="12" t="n"/>
-      <c r="R336" s="12" t="n"/>
-      <c r="S336" s="12" t="n"/>
-      <c r="T336" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U336" s="12" t="n"/>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>operating_company_treasury</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr"/>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>https://lei.jpx.co.jp/lei/en/detail.html?lei=3538004SYEDMHPTGRC96</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -47698,6 +48333,11 @@
       <c r="C337" t="inlineStr">
         <is>
           <t>Gagandeep Credit Capital Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
         </is>
       </c>
       <c r="E337" s="2" t="n">
@@ -47712,25 +48352,37 @@
       <c r="L337" s="2" t="n"/>
       <c r="M337" s="2" t="n"/>
       <c r="N337" s="2" t="n"/>
-      <c r="O337" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P337" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q337" s="12" t="n"/>
-      <c r="R337" s="12" t="n"/>
-      <c r="S337" s="12" t="n"/>
-      <c r="T337" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U337" s="12" t="n"/>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr"/>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>https://www.thecompanycheck.com/company/gagandeep-credit-capital-private-limited/U65990MH1993PTC073769</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -47746,6 +48398,11 @@
       <c r="C338" t="inlineStr">
         <is>
           <t>Enam Securities Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
         </is>
       </c>
       <c r="E338" s="2" t="n">
@@ -47760,25 +48417,37 @@
       <c r="L338" s="2" t="n"/>
       <c r="M338" s="2" t="n"/>
       <c r="N338" s="2" t="n"/>
-      <c r="O338" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P338" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q338" s="12" t="n"/>
-      <c r="R338" s="12" t="n"/>
-      <c r="S338" s="12" t="n"/>
-      <c r="T338" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U338" s="12" t="n"/>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr"/>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>https://indiafilings.com/search/enam-securities-private-limited-cin-u67120mh2005ptc152297</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -47794,6 +48463,11 @@
       <c r="C339" t="inlineStr">
         <is>
           <t>Shamyak Investment Private Limited</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
         </is>
       </c>
       <c r="E339" s="2" t="n">
@@ -47808,25 +48482,37 @@
       <c r="L339" s="2" t="n"/>
       <c r="M339" s="2" t="n"/>
       <c r="N339" s="2" t="n"/>
-      <c r="O339" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P339" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q339" s="12" t="n"/>
-      <c r="R339" s="12" t="n"/>
-      <c r="S339" s="12" t="n"/>
-      <c r="T339" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U339" s="12" t="n"/>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr"/>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>https://www.instafinancials.com/company/shamyak-investment-private-limited-u23201mh1983ptc031175/</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -48494,6 +49180,11 @@
           <t>GOVERNMENT OF SINGAPORE</t>
         </is>
       </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="E350" s="2" t="n">
         <v>21502855</v>
       </c>
@@ -48506,25 +49197,37 @@
       <c r="L350" s="2" t="n"/>
       <c r="M350" s="2" t="n"/>
       <c r="N350" s="2" t="n"/>
-      <c r="O350" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P350" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q350" s="12" t="n"/>
-      <c r="R350" s="12" t="n"/>
-      <c r="S350" s="12" t="n"/>
-      <c r="T350" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U350" s="12" t="n"/>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr"/>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -48540,6 +49243,11 @@
       <c r="C351" t="inlineStr">
         <is>
           <t>L&amp;T EMPLOYEES TRUST</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
         </is>
       </c>
       <c r="E351" s="2" t="n">
@@ -48554,25 +49262,37 @@
       <c r="L351" s="2" t="n"/>
       <c r="M351" s="2" t="n"/>
       <c r="N351" s="2" t="n"/>
-      <c r="O351" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P351" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q351" s="12" t="n"/>
-      <c r="R351" s="12" t="n"/>
-      <c r="S351" s="12" t="n"/>
-      <c r="T351" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U351" s="12" t="n"/>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr"/>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>https://sebi.gov.in/sebi-data/docfiles/11754_t.html</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -51105,6 +51825,11 @@
           <t>Government Of Singapore</t>
         </is>
       </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="E395" s="2" t="n"/>
       <c r="F395" s="2" t="n"/>
       <c r="G395" s="2" t="n"/>
@@ -51117,25 +51842,37 @@
         <v>197673526</v>
       </c>
       <c r="N395" s="2" t="n"/>
-      <c r="O395" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P395" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q395" s="12" t="n"/>
-      <c r="R395" s="12" t="n"/>
-      <c r="S395" s="12" t="n"/>
-      <c r="T395" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U395" s="12" t="n"/>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr"/>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -51598,6 +52335,11 @@
           <t>GOVERNMENT OF SINGAPORE</t>
         </is>
       </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="E403" s="2" t="n">
         <v>164016397</v>
       </c>
@@ -51610,25 +52352,37 @@
       <c r="L403" s="2" t="n"/>
       <c r="M403" s="2" t="n"/>
       <c r="N403" s="2" t="n"/>
-      <c r="O403" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="P403" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q403" s="12" t="n"/>
-      <c r="R403" s="12" t="n"/>
-      <c r="S403" s="12" t="n"/>
-      <c r="T403" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U403" s="12" t="n"/>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr"/>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -55220,7 +55974,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Foreign Pension Fund</t>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="E466" s="2" t="n">
@@ -55235,39 +55989,35 @@
       <c r="L466" s="2" t="n"/>
       <c r="M466" s="2" t="n"/>
       <c r="N466" s="2" t="n"/>
-      <c r="O466" s="12" t="inlineStr">
+      <c r="O466" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="P466" s="12" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="Q466" s="12" t="inlineStr">
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="R466" s="12" t="inlineStr">
-        <is>
-          <t>pension_fund</t>
-        </is>
-      </c>
-      <c r="S466" s="12" t="inlineStr">
-        <is>
-          <t>pension_assets</t>
-        </is>
-      </c>
-      <c r="T466" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U466" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nbim.no/</t>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr"/>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Government_Pension_Fund_of_Norway</t>
         </is>
       </c>
     </row>
@@ -56399,29 +57149,23 @@
         <v>555000000</v>
       </c>
       <c r="N482" s="2" t="n"/>
-      <c r="O482" s="12" t="inlineStr">
+      <c r="O482" t="inlineStr">
         <is>
           <t>filing (token+numeric)</t>
         </is>
       </c>
-      <c r="P482" s="12" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q482" s="12" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="R482" s="12" t="n"/>
-      <c r="S482" s="12" t="n"/>
-      <c r="T482" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U482" s="12" t="inlineStr">
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr"/>
+      <c r="U482" t="inlineStr">
         <is>
           <t>SEBI LODR Reg 31 shareholding pattern (Table II - Promoter &amp; Promoter Group), as at 2025-09-30</t>
         </is>
@@ -58935,37 +59679,33 @@
         <v>150607989</v>
       </c>
       <c r="N528" s="2" t="n"/>
-      <c r="O528" s="12" t="inlineStr">
+      <c r="O528" t="inlineStr">
         <is>
           <t>rule:amc+india</t>
         </is>
       </c>
-      <c r="P528" s="12" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q528" s="12" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="R528" s="12" t="inlineStr">
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="R528" t="inlineStr">
         <is>
           <t>asset_manager</t>
         </is>
       </c>
-      <c r="S528" s="12" t="inlineStr">
+      <c r="S528" t="inlineStr">
         <is>
           <t>managed_funds</t>
         </is>
       </c>
-      <c r="T528" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U528" s="12" t="inlineStr">
+      <c r="T528" t="inlineStr"/>
+      <c r="U528" t="inlineStr">
         <is>
           <t>matched by deterministic name rule</t>
         </is>
@@ -59004,37 +59744,33 @@
         <v>40680381</v>
       </c>
       <c r="N529" s="2" t="n"/>
-      <c r="O529" s="12" t="inlineStr">
+      <c r="O529" t="inlineStr">
         <is>
           <t>rule:amc+india</t>
         </is>
       </c>
-      <c r="P529" s="12" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q529" s="12" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="R529" s="12" t="inlineStr">
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="R529" t="inlineStr">
         <is>
           <t>asset_manager</t>
         </is>
       </c>
-      <c r="S529" s="12" t="inlineStr">
+      <c r="S529" t="inlineStr">
         <is>
           <t>managed_funds</t>
         </is>
       </c>
-      <c r="T529" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U529" s="12" t="inlineStr">
+      <c r="T529" t="inlineStr"/>
+      <c r="U529" t="inlineStr">
         <is>
           <t>matched by deterministic name rule</t>
         </is>
@@ -59073,37 +59809,33 @@
         <v>40518952</v>
       </c>
       <c r="N530" s="2" t="n"/>
-      <c r="O530" s="12" t="inlineStr">
+      <c r="O530" t="inlineStr">
         <is>
           <t>rule:amc+india</t>
         </is>
       </c>
-      <c r="P530" s="12" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q530" s="12" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="R530" s="12" t="inlineStr">
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
         <is>
           <t>asset_manager</t>
         </is>
       </c>
-      <c r="S530" s="12" t="inlineStr">
+      <c r="S530" t="inlineStr">
         <is>
           <t>managed_funds</t>
         </is>
       </c>
-      <c r="T530" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="U530" s="12" t="inlineStr">
+      <c r="T530" t="inlineStr"/>
+      <c r="U530" t="inlineStr">
         <is>
           <t>matched by deterministic name rule</t>
         </is>
@@ -59142,33 +59874,37 @@
         <v>121567690</v>
       </c>
       <c r="N531" s="2" t="n"/>
-      <c r="O531" t="inlineStr">
+      <c r="O531" s="12" t="inlineStr">
         <is>
           <t>rule:amc+india</t>
         </is>
       </c>
-      <c r="P531" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q531" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="R531" t="inlineStr">
+      <c r="P531" s="12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q531" s="12" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="R531" s="12" t="inlineStr">
         <is>
           <t>asset_manager</t>
         </is>
       </c>
-      <c r="S531" t="inlineStr">
+      <c r="S531" s="12" t="inlineStr">
         <is>
           <t>managed_funds</t>
         </is>
       </c>
-      <c r="T531" t="inlineStr"/>
-      <c r="U531" t="inlineStr">
+      <c r="T531" s="12" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="U531" s="12" t="inlineStr">
         <is>
           <t>matched by deterministic name rule</t>
         </is>
@@ -59207,33 +59943,37 @@
         <v>137781580</v>
       </c>
       <c r="N532" s="2" t="n"/>
-      <c r="O532" t="inlineStr">
+      <c r="O532" s="12" t="inlineStr">
         <is>
           <t>rule:indian-pension-scheme</t>
         </is>
       </c>
-      <c r="P532" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q532" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="R532" t="inlineStr">
+      <c r="P532" s="12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q532" s="12" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="R532" s="12" t="inlineStr">
         <is>
           <t>pension_fund</t>
         </is>
       </c>
-      <c r="S532" t="inlineStr">
+      <c r="S532" s="12" t="inlineStr">
         <is>
           <t>pension_assets</t>
         </is>
       </c>
-      <c r="T532" t="inlineStr"/>
-      <c r="U532" t="inlineStr">
+      <c r="T532" s="12" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="U532" s="12" t="inlineStr">
         <is>
           <t>matched by deterministic name rule</t>
         </is>
@@ -59253,6 +59993,11 @@
       <c r="C533" t="inlineStr">
         <is>
           <t>GOVERNMENT OF SINGAPORE</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="E533" s="2" t="n"/>
@@ -59264,28 +60009,44 @@
       <c r="K533" s="2" t="n"/>
       <c r="L533" s="2" t="n"/>
       <c r="M533" s="2" t="n">
-        <v>2134450960</v>
+        <v>213446728</v>
       </c>
       <c r="N533" s="2" t="n"/>
       <c r="O533" s="12" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="P533" s="12" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q533" s="12" t="n"/>
-      <c r="R533" s="12" t="n"/>
-      <c r="S533" s="12" t="n"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q533" s="12" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="R533" s="12" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="S533" s="12" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
       <c r="T533" s="12" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="U533" s="12" t="n"/>
+      <c r="U533" s="12" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -59301,6 +60062,11 @@
       <c r="C534" t="inlineStr">
         <is>
           <t>MACRITCHIE INVESTMENTS PTE LTD</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
         </is>
       </c>
       <c r="E534" s="2" t="n"/>
@@ -59317,23 +60083,39 @@
       <c r="N534" s="2" t="n"/>
       <c r="O534" s="12" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="P534" s="12" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q534" s="12" t="n"/>
-      <c r="R534" s="12" t="n"/>
-      <c r="S534" s="12" t="n"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q534" s="12" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="R534" s="12" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="S534" s="12" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
       <c r="T534" s="12" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="U534" s="12" t="n"/>
+      <c r="U534" s="12" t="inlineStr">
+        <is>
+          <t>https://www.crunchbase.com/organization/macritchie-investments</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -61102,29 +61884,46 @@
           <t>Government of Singapore</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
         <v>80899294</v>
       </c>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="n"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -61676,29 +62475,46 @@
           <t>Google International LLC</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
         <v>71176839</v>
       </c>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="n"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>operating_company_treasury</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/1288776/000119312507044494/dex2101.htm</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -61711,29 +62527,50 @@
           <t>Government of Singapore - E</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Foreign Government</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
         <v>64377450</v>
       </c>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="L11" s="12" t="n"/>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>https://ifswf.org/member-profiles/government-singapore-investment-corporation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -61748,46 +62585,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Foreign Pension Fund</t>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>61036886</v>
       </c>
       <c r="E12" s="2" t="n"/>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>pension_fund</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>pension_assets</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L12" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nbim.no/</t>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Government_Pension_Fund_of_Norway</t>
         </is>
       </c>
     </row>
@@ -62489,46 +63322,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Foreign Pension Fund</t>
+          <t>Foreign Government</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
         <v>10431209</v>
       </c>
       <c r="E13" s="2" t="n"/>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>pension_fund</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>pension_assets</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nbim.no/</t>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>sovereign_wealth_fund</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>sovereign_assets</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Government_Pension_Fund_of_Norway</t>
         </is>
       </c>
     </row>
@@ -62543,29 +63372,46 @@
           <t>Vanguard Total International Stock Index Fund</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
         <v>8394985</v>
       </c>
       <c r="E14" s="2" t="n"/>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="n"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/736054/000168386322001087/f11043d1.htm</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
